--- a/Документы/Список для рассылки.xlsx
+++ b/Документы/Список для рассылки.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHub\RollPrint\Документы\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -15,7 +15,7 @@
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Лист1!$B$668:$D$707</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Лист1!$B$709:$D$737</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="678" uniqueCount="670">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="707" uniqueCount="685">
   <si>
     <t>Автозаводец №6</t>
   </si>
@@ -2037,6 +2037,51 @@
   </si>
   <si>
     <t>Работа для вас №74</t>
+  </si>
+  <si>
+    <t>Ашмянски весник №49</t>
+  </si>
+  <si>
+    <t>Астравецкая прауда №49</t>
+  </si>
+  <si>
+    <t>Родны край №48</t>
+  </si>
+  <si>
+    <t>Азбука дома №25</t>
+  </si>
+  <si>
+    <t>Перамога №50</t>
+  </si>
+  <si>
+    <t>Регион №51</t>
+  </si>
+  <si>
+    <t>ПАК №26</t>
+  </si>
+  <si>
+    <t>Женская газета №26</t>
+  </si>
+  <si>
+    <t>Досуг пенсионера №26</t>
+  </si>
+  <si>
+    <t>Маладзечанская газета №47</t>
+  </si>
+  <si>
+    <t>Астравецкая прауда №50</t>
+  </si>
+  <si>
+    <t>Шлях перамоги №47</t>
+  </si>
+  <si>
+    <t>Слава працы №47</t>
+  </si>
+  <si>
+    <t>Перамога №51</t>
+  </si>
+  <si>
+    <t>Приглашаем на работу №26</t>
   </si>
 </sst>
 </file>
@@ -2122,7 +2167,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -2146,6 +2191,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2427,7 +2475,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B2:D707"/>
+  <dimension ref="B2:D737"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="4.140625" customWidth="1"/>
@@ -8530,6 +8578,267 @@
         <v>32</v>
       </c>
     </row>
+    <row r="709" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B709" s="2"/>
+      <c r="C709" s="3">
+        <v>885</v>
+      </c>
+      <c r="D709" s="2" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="710" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B710" s="2"/>
+      <c r="C710" s="3">
+        <v>886</v>
+      </c>
+      <c r="D710" s="2" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="711" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B711" s="2"/>
+      <c r="C711" s="3">
+        <v>887</v>
+      </c>
+      <c r="D711" s="2" t="s">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="712" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B712" s="2"/>
+      <c r="C712" s="3">
+        <v>888</v>
+      </c>
+      <c r="D712" s="2" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="713" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B713" s="2"/>
+      <c r="C713" s="3">
+        <v>889</v>
+      </c>
+      <c r="D713" s="2" t="s">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="714" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B714" s="2"/>
+      <c r="C714" s="3">
+        <v>890</v>
+      </c>
+      <c r="D714" s="2" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="715" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B715" s="2"/>
+      <c r="C715" s="3">
+        <v>891</v>
+      </c>
+      <c r="D715" s="2" t="s">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="716" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B716" s="2"/>
+      <c r="C716" s="3">
+        <v>892</v>
+      </c>
+      <c r="D716" s="2" t="s">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="717" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B717" s="2"/>
+      <c r="C717" s="3">
+        <v>893</v>
+      </c>
+      <c r="D717" s="2" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="718" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B718" s="2"/>
+      <c r="C718" s="3">
+        <v>894</v>
+      </c>
+      <c r="D718" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="719" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B719" s="2"/>
+      <c r="C719" s="10">
+        <v>895</v>
+      </c>
+      <c r="D719" s="2" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="720" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B720" s="2"/>
+      <c r="C720" s="10">
+        <v>896</v>
+      </c>
+      <c r="D720" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="721" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B721" s="2"/>
+      <c r="C721" s="10">
+        <v>897</v>
+      </c>
+      <c r="D721" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="722" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B722" s="2"/>
+      <c r="C722" s="10">
+        <v>898</v>
+      </c>
+      <c r="D722" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="723" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B723" s="2"/>
+      <c r="C723" s="10">
+        <v>899</v>
+      </c>
+      <c r="D723" s="2" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="724" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B724" s="2"/>
+      <c r="C724" s="10">
+        <v>900</v>
+      </c>
+      <c r="D724" s="2" t="s">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="725" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B725" s="2"/>
+      <c r="C725" s="10">
+        <v>901</v>
+      </c>
+      <c r="D725" s="2" t="s">
+        <v>682</v>
+      </c>
+    </row>
+    <row r="726" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B726" s="2"/>
+      <c r="C726" s="10">
+        <v>902</v>
+      </c>
+      <c r="D726" s="2" t="s">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="727" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B727" s="2"/>
+      <c r="C727" s="10">
+        <v>903</v>
+      </c>
+      <c r="D727" s="2" t="s">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="728" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B728" s="2"/>
+      <c r="C728" s="10">
+        <v>904</v>
+      </c>
+      <c r="D728" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="729" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B729" s="2"/>
+      <c r="C729" s="10">
+        <v>905</v>
+      </c>
+      <c r="D729" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="730" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B730" s="2"/>
+      <c r="C730" s="10">
+        <v>906</v>
+      </c>
+      <c r="D730" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="731" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B731" s="2"/>
+      <c r="C731" s="10">
+        <v>907</v>
+      </c>
+      <c r="D731" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="732" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B732" s="2"/>
+      <c r="C732" s="10">
+        <v>908</v>
+      </c>
+      <c r="D732" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="733" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B733" s="2"/>
+      <c r="C733" s="10">
+        <v>909</v>
+      </c>
+      <c r="D733" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="734" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B734" s="2"/>
+      <c r="C734" s="10">
+        <v>910</v>
+      </c>
+      <c r="D734" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="735" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B735" s="2"/>
+      <c r="C735" s="10">
+        <v>911</v>
+      </c>
+      <c r="D735" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="736" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B736" s="2"/>
+      <c r="C736" s="10">
+        <v>912</v>
+      </c>
+      <c r="D736" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="737" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B737" s="2"/>
+      <c r="C737" s="10">
+        <v>913</v>
+      </c>
+      <c r="D737" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
